--- a/data/trans_orig/P36B14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016</t>
+          <t>Población según la frecuencia de consumo de refrescos con azúcar en 2016 (tasa de respuesta: 99,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>218707</t>
+          <t>220647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>269275</t>
+          <t>268395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238178</t>
+          <t>239928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289276</t>
+          <t>290772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>474324</t>
+          <t>471981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>544750</t>
+          <t>543353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,56%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103246</t>
+          <t>103180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145584</t>
+          <t>144264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92255</t>
+          <t>92089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129598</t>
+          <t>129899</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208485</t>
+          <t>208518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>261752</t>
+          <t>263000</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96315</t>
+          <t>96812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136555</t>
+          <t>136248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110052</t>
+          <t>108906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149467</t>
+          <t>149850</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>216029</t>
+          <t>215675</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>272201</t>
+          <t>269937</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98490</t>
+          <t>100592</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139471</t>
+          <t>139849</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78985</t>
+          <t>81276</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114611</t>
+          <t>117321</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191632</t>
+          <t>191559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244866</t>
+          <t>244638</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55495</t>
+          <t>55067</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87672</t>
+          <t>88086</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54316</t>
+          <t>53149</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>83796</t>
+          <t>85640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117394</t>
+          <t>116479</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162169</t>
+          <t>164357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271321</t>
+          <t>271548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>330329</t>
+          <t>328460</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>326546</t>
+          <t>326070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>389551</t>
+          <t>388047</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>618732</t>
+          <t>614251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>703421</t>
+          <t>708107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123036</t>
+          <t>122426</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171492</t>
+          <t>167235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>138986</t>
+          <t>140921</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>189160</t>
+          <t>190513</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>279124</t>
+          <t>277541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>344662</t>
+          <t>344464</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>176187</t>
+          <t>174238</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>229498</t>
+          <t>226919</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>176014</t>
+          <t>178354</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>227301</t>
+          <t>229531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>368559</t>
+          <t>365760</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>438619</t>
+          <t>438424</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172635</t>
+          <t>175688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223734</t>
+          <t>225713</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155559</t>
+          <t>156060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204409</t>
+          <t>204823</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341501</t>
+          <t>342576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414969</t>
+          <t>417206</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151439</t>
+          <t>151463</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>201730</t>
+          <t>202246</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>116381</t>
+          <t>119219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159643</t>
+          <t>162178</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279984</t>
+          <t>279267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>351036</t>
+          <t>346663</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>189682</t>
+          <t>187110</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239365</t>
+          <t>239271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>234822</t>
+          <t>236697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288803</t>
+          <t>290572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>440961</t>
+          <t>436966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>515001</t>
+          <t>514027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96730</t>
+          <t>98338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137804</t>
+          <t>138800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105799</t>
+          <t>104019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146264</t>
+          <t>146181</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213712</t>
+          <t>214451</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>271851</t>
+          <t>274177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122744</t>
+          <t>123889</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>169632</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>101999</t>
+          <t>102157</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>143225</t>
+          <t>143242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>234809</t>
+          <t>238592</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>298592</t>
+          <t>299441</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>128709</t>
+          <t>127505</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>176214</t>
+          <t>173546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>114570</t>
+          <t>112006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>155664</t>
+          <t>157103</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>250763</t>
+          <t>250771</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>313546</t>
+          <t>314533</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111872</t>
+          <t>111379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153981</t>
+          <t>156612</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114074</t>
+          <t>114577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156236</t>
+          <t>157699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>237406</t>
+          <t>238418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>298373</t>
+          <t>301271</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>283892</t>
+          <t>282012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>340478</t>
+          <t>341203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>382502</t>
+          <t>384883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>448916</t>
+          <t>448881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>685180</t>
+          <t>685498</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>773511</t>
+          <t>772665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127836</t>
+          <t>128736</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>172265</t>
+          <t>173466</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>161146</t>
+          <t>164456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>212412</t>
+          <t>214423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>302668</t>
+          <t>299750</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>373413</t>
+          <t>372172</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,0%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>135090</t>
+          <t>135194</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>178970</t>
+          <t>181124</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>131393</t>
+          <t>129878</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>176591</t>
+          <t>176433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>277833</t>
+          <t>273020</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>343404</t>
+          <t>340072</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135216</t>
+          <t>136905</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180878</t>
+          <t>181350</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>130518</t>
+          <t>128174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175364</t>
+          <t>173705</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>280089</t>
+          <t>280228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>342996</t>
+          <t>345478</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,64%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>129073</t>
+          <t>127478</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170988</t>
+          <t>171777</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>107257</t>
+          <t>104937</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149973</t>
+          <t>148439</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>244551</t>
+          <t>244595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>305360</t>
+          <t>306995</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1009521</t>
+          <t>1016057</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1121586</t>
+          <t>1124840</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1236228</t>
+          <t>1241152</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1357265</t>
+          <t>1357914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2289214</t>
+          <t>2291401</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2439943</t>
+          <t>2452599</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>488272</t>
+          <t>493512</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>579916</t>
+          <t>579744</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>541441</t>
+          <t>541756</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>631440</t>
+          <t>632915</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1055100</t>
+          <t>1060499</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1185675</t>
+          <t>1183688</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>569173</t>
+          <t>572154</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>661902</t>
+          <t>665401</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>559677</t>
+          <t>563244</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>651913</t>
+          <t>652079</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1163119</t>
+          <t>1161984</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1285691</t>
+          <t>1295175</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>586150</t>
+          <t>582041</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>674847</t>
+          <t>677375</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>520070</t>
+          <t>514636</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>609413</t>
+          <t>608232</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1127649</t>
+          <t>1130901</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1254806</t>
+          <t>1254060</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>483864</t>
+          <t>481946</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>572674</t>
+          <t>570117</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>430332</t>
+          <t>429255</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>509047</t>
+          <t>507796</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>935650</t>
+          <t>933163</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1053818</t>
+          <t>1049478</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B14-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>220647</t>
+          <t>216717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>268395</t>
+          <t>268409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>239928</t>
+          <t>239508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>290772</t>
+          <t>290298</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>471981</t>
+          <t>472024</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>543353</t>
+          <t>541705</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103180</t>
+          <t>104115</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144264</t>
+          <t>144409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92089</t>
+          <t>92876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129899</t>
+          <t>129612</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>208518</t>
+          <t>206588</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>263000</t>
+          <t>260738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96812</t>
+          <t>95707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136248</t>
+          <t>136527</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108906</t>
+          <t>108428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149850</t>
+          <t>149637</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>215675</t>
+          <t>215456</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>269937</t>
+          <t>269930</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100592</t>
+          <t>101371</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139849</t>
+          <t>143463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81276</t>
+          <t>81674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117321</t>
+          <t>117956</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>191559</t>
+          <t>190629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>244638</t>
+          <t>245942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55067</t>
+          <t>55198</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88086</t>
+          <t>88064</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53149</t>
+          <t>53504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85640</t>
+          <t>84070</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>117257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>164357</t>
+          <t>163529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>271548</t>
+          <t>269248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>328460</t>
+          <t>326776</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>326070</t>
+          <t>322525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>388047</t>
+          <t>389336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>614251</t>
+          <t>613444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>708107</t>
+          <t>700963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122426</t>
+          <t>121549</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167235</t>
+          <t>169434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>140921</t>
+          <t>140299</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>190513</t>
+          <t>188967</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>277541</t>
+          <t>278200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>344464</t>
+          <t>346124</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174238</t>
+          <t>175219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>226919</t>
+          <t>228073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>178354</t>
+          <t>173074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229531</t>
+          <t>229587</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>365760</t>
+          <t>364330</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>438424</t>
+          <t>439159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>175688</t>
+          <t>174528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225713</t>
+          <t>221877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156060</t>
+          <t>158152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204823</t>
+          <t>207326</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342576</t>
+          <t>345813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>417206</t>
+          <t>420120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151463</t>
+          <t>151744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202246</t>
+          <t>201375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>119219</t>
+          <t>118303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162178</t>
+          <t>162394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>279267</t>
+          <t>283461</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346663</t>
+          <t>346009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>187110</t>
+          <t>187434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>239271</t>
+          <t>240693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>236697</t>
+          <t>237268</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>290572</t>
+          <t>291560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436966</t>
+          <t>439993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>514027</t>
+          <t>511584</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>98338</t>
+          <t>96374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>138800</t>
+          <t>139564</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>104019</t>
+          <t>104542</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146181</t>
+          <t>145485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214451</t>
+          <t>214222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274177</t>
+          <t>270303</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123889</t>
+          <t>124274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>169632</t>
+          <t>169236</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102157</t>
+          <t>102859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>143242</t>
+          <t>145808</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>238592</t>
+          <t>236576</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>299441</t>
+          <t>295634</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>127505</t>
+          <t>128192</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>173546</t>
+          <t>172906</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112006</t>
+          <t>113667</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>157103</t>
+          <t>157978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>250771</t>
+          <t>254483</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>314533</t>
+          <t>315150</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>111379</t>
+          <t>112143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>156612</t>
+          <t>156248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114577</t>
+          <t>112770</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>157699</t>
+          <t>156456</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238418</t>
+          <t>235912</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>301271</t>
+          <t>295673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>282012</t>
+          <t>282719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>341203</t>
+          <t>342373</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>384883</t>
+          <t>385235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>448881</t>
+          <t>448775</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>685498</t>
+          <t>683769</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>772665</t>
+          <t>768699</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>127369</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>173466</t>
+          <t>172568</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>164456</t>
+          <t>162900</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>214423</t>
+          <t>215638</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>299750</t>
+          <t>303425</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>372172</t>
+          <t>372553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>135194</t>
+          <t>135812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>181124</t>
+          <t>182433</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,47 +3017,47 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>19,73%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>151163</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>128534</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>173292</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>14,62%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>19,59%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>151163</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>129878</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>176433</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>14,62%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>273020</t>
+          <t>274834</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>340072</t>
+          <t>338533</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136905</t>
+          <t>136235</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>181350</t>
+          <t>180747</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128174</t>
+          <t>132009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>173705</t>
+          <t>177321</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>280228</t>
+          <t>277067</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>345478</t>
+          <t>343253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>127478</t>
+          <t>128883</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171777</t>
+          <t>173645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>104937</t>
+          <t>107179</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148439</t>
+          <t>148928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>244595</t>
+          <t>243049</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>306995</t>
+          <t>308822</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1016057</t>
+          <t>1013835</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1124840</t>
+          <t>1124029</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1241152</t>
+          <t>1239405</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1357914</t>
+          <t>1356050</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2291401</t>
+          <t>2288910</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2452599</t>
+          <t>2445072</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>493512</t>
+          <t>487730</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>579744</t>
+          <t>580383</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>541756</t>
+          <t>545281</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>632915</t>
+          <t>631415</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1060499</t>
+          <t>1052328</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1183688</t>
+          <t>1181943</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>572154</t>
+          <t>571734</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>665401</t>
+          <t>662270</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>563244</t>
+          <t>558737</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>652079</t>
+          <t>652614</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1161984</t>
+          <t>1160180</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1295175</t>
+          <t>1285395</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>582041</t>
+          <t>582847</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>677375</t>
+          <t>676407</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>514636</t>
+          <t>522344</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>608232</t>
+          <t>610335</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1130901</t>
+          <t>1125167</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1254060</t>
+          <t>1253831</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>481946</t>
+          <t>484555</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>570117</t>
+          <t>567761</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>429255</t>
+          <t>429029</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>507796</t>
+          <t>507925</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>933163</t>
+          <t>931751</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1049478</t>
+          <t>1054926</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
